--- a/correlations.xlsx
+++ b/correlations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/PhD/paper6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FD3C78-77C7-024E-B79D-054F61AF5FB9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94A2C01-A8BB-4C47-8202-FF0A8DD69D5C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -289,10 +289,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -310,6 +310,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>177155</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{516A1B55-27D0-EB46-BCDC-B6C5E765EDFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4724400" y="0"/>
+          <a:ext cx="4813300" cy="3606155"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -970,5 +1025,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>